--- a/Intersecciones/excels/UCAYALI-CORONEL_PORTILLO-MANANTAY.xlsx
+++ b/Intersecciones/excels/UCAYALI-CORONEL_PORTILLO-MANANTAY.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,7 +483,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>l-132509</t>
+          <t>I-20988</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -508,22 +508,22 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-8.3996103</t>
+          <t>-8.4008518</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-74.5347843</t>
+          <t>-74.5388106</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Los Ceticos</t>
+          <t>Atalaya / Avenida Túpac Amaru</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -535,7 +535,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>l-21234</t>
+          <t>I-132509</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -560,17 +560,17 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-8.4058702</t>
+          <t>-8.3996103</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-74.5540731</t>
+          <t>-74.5347843</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Los Laureles</t>
+          <t>Los Ceticos / Calle s / n</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -587,7 +587,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>l-248682</t>
+          <t>I-20959</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -612,22 +612,22 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-8.3982765</t>
+          <t>-8.3966189</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-74.5599596</t>
+          <t>-74.5331103</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Avenida Túpac Amaru</t>
+          <t>Las Palmeras / Calle s / n</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -639,7 +639,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>l-248683</t>
+          <t>I-254761</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -664,25 +664,1013 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-8.3982801</t>
+          <t>-8.3998756</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-74.5598062</t>
+          <t>-74.5429416</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Avenida Túpac Amaru</t>
+          <t>Avenida Túpac Amaru / Calle s / n</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
+        <is>
+          <t>250107</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>I-255363</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>250107</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>CORONEL PORTILLO</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>MANANTAY</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>-8.4286936</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-74.5723062</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Habilitación Urbana Municipal / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>250107</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>I-255361</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>250107</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>CORONEL PORTILLO</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>MANANTAY</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>-8.4290844</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-74.5736614</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>250107</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>I-255360</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>250107</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>CORONEL PORTILLO</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>MANANTAY</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>-8.426421</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-74.5720761</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>250107</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>I-255359</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>250107</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>CORONEL PORTILLO</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>MANANTAY</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>-8.4272363</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-74.57492</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>250107</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>I-255358</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>250107</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>CORONEL PORTILLO</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>MANANTAY</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>-8.4286205</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-74.5774125</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>250107</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>I-255356</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>250107</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>CORONEL PORTILLO</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>MANANTAY</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>-8.4281068</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-74.5765927</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>250107</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>I-255349</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>250107</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>CORONEL PORTILLO</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>MANANTAY</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>-8.4268849</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-74.5735978</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>250107</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>I-255330</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>250107</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>CORONEL PORTILLO</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>MANANTAY</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>-8.408309</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-74.5603664</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Avenida Aviación / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>250107</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>I-255347</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>250107</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>CORONEL PORTILLO</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>MANANTAY</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>-8.435271</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-74.5725605</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>250107</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>I-255345</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>250107</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>CORONEL PORTILLO</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>MANANTAY</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>-8.4373081</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-74.5719764</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>250107</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>I-255344</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>250107</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>CORONEL PORTILLO</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>MANANTAY</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>-8.4317467</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-74.5735649</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>250107</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>I-255343</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>250107</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>CORONEL PORTILLO</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>MANANTAY</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>-8.4332729</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-74.5731073</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>250107</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>I-255336</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>250107</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>CORONEL PORTILLO</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>MANANTAY</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>-8.4203477</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-74.5481956</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>250107</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>I-263081</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>250107</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>CORONEL PORTILLO</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>MANANTAY</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>-8.549242</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-74.363363</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>250107</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>I-255377</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>250107</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>CORONEL PORTILLO</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>MANANTAY</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>-8.4279031</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-74.5733124</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>250107</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>I-255378</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>250107</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>CORONEL PORTILLO</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>MANANTAY</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>-8.429883</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-74.5727296</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>250107</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>I-255379</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>250107</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>CORONEL PORTILLO</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>MANANTAY</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>-8.4349401</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-74.5713123</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>250107</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>I-255381</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>250107</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>CORONEL PORTILLO</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>MANANTAY</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>-8.425312</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-74.5733048</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Habilitación Urbana Municipal / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>250107</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>I-263082</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>250107</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>CORONEL PORTILLO</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>MANANTAY</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>-8.5500674</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-74.3639573</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
         <is>
           <t>250107</t>
         </is>

--- a/Intersecciones/excels/UCAYALI-CORONEL_PORTILLO-MANANTAY.xlsx
+++ b/Intersecciones/excels/UCAYALI-CORONEL_PORTILLO-MANANTAY.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1676,6 +1676,266 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>I-8353</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>250107</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>CORONEL PORTILLO</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>MANANTAY</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>-8.3970341</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-74.5490772</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Avenida Colonización / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>250107</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>I-255365</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>250107</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>CORONEL PORTILLO</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>MANANTAY</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>-8.425688</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-74.5746229</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>250107</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>I-255331</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>250107</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>CORONEL PORTILLO</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>MANANTAY</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>-8.4126675</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-74.5397995</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>250107</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>I-255332</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>250107</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>CORONEL PORTILLO</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>MANANTAY</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>-8.4151389</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-74.5553027</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>250107</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>I-255334</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>250107</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>CORONEL PORTILLO</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>MANANTAY</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>-8.4203493</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-74.5468338</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>250107</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Intersecciones/excels/UCAYALI-CORONEL_PORTILLO-MANANTAY.xlsx
+++ b/Intersecciones/excels/UCAYALI-CORONEL_PORTILLO-MANANTAY.xlsx
@@ -425,35 +425,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>ubigeo_gestor</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>PROVINCIA</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>DISTRITO</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>ID_INT</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>UBIGEO</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>DEPARTAMENTO</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>PROVINCIA</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>DISTRITO</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>LATITUD</t>
@@ -472,40 +472,35 @@
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Siniestro_fatal</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>ubigeo_gestor</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>250107</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CORONEL_PORTILLO</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>MANANTAY</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>I-20988</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>250107</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>UCAYALI</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>CORONEL PORTILLO</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>MANANTAY</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>-8.4008518</t>
@@ -524,40 +519,35 @@
       <c r="I2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>250107</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>250107</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CORONEL_PORTILLO</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>MANANTAY</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>I-132509</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>250107</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>UCAYALI</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>CORONEL PORTILLO</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>MANANTAY</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>-8.3996103</t>
@@ -576,40 +566,35 @@
       <c r="I3" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>250107</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>250107</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CORONEL_PORTILLO</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>MANANTAY</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>I-20959</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>250107</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>UCAYALI</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>CORONEL PORTILLO</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>MANANTAY</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>-8.3966189</t>
@@ -628,40 +613,35 @@
       <c r="I4" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>250107</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>250107</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CORONEL_PORTILLO</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>MANANTAY</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>I-254761</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>250107</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>UCAYALI</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>CORONEL PORTILLO</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>MANANTAY</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>-8.3998756</t>
@@ -680,40 +660,35 @@
       <c r="I5" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>250107</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>250107</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CORONEL_PORTILLO</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>MANANTAY</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>I-255363</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>250107</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>UCAYALI</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>CORONEL PORTILLO</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>MANANTAY</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>-8.4286936</t>
@@ -732,40 +707,35 @@
       <c r="I6" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>250107</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>250107</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CORONEL_PORTILLO</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>MANANTAY</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>I-255361</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>250107</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>UCAYALI</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>CORONEL PORTILLO</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>MANANTAY</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>-8.4290844</t>
@@ -784,40 +754,35 @@
       <c r="I7" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>250107</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>250107</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CORONEL_PORTILLO</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>MANANTAY</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>I-255360</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>250107</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>UCAYALI</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>CORONEL PORTILLO</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>MANANTAY</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>-8.426421</t>
@@ -836,40 +801,35 @@
       <c r="I8" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>250107</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>250107</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CORONEL_PORTILLO</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>MANANTAY</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>I-255359</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>250107</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>UCAYALI</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>CORONEL PORTILLO</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>MANANTAY</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>-8.4272363</t>
@@ -888,40 +848,35 @@
       <c r="I9" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>250107</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>250107</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CORONEL_PORTILLO</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>MANANTAY</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>I-255358</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>250107</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>UCAYALI</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>CORONEL PORTILLO</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>MANANTAY</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>-8.4286205</t>
@@ -940,40 +895,35 @@
       <c r="I10" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>250107</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>250107</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CORONEL_PORTILLO</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>MANANTAY</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>I-255356</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>250107</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>UCAYALI</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>CORONEL PORTILLO</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>MANANTAY</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>-8.4281068</t>
@@ -992,40 +942,35 @@
       <c r="I11" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>250107</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>250107</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CORONEL_PORTILLO</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>MANANTAY</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>I-255349</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>250107</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>UCAYALI</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>CORONEL PORTILLO</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>MANANTAY</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>-8.4268849</t>
@@ -1044,40 +989,35 @@
       <c r="I12" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>250107</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>250107</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CORONEL_PORTILLO</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>MANANTAY</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>I-255330</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>250107</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>UCAYALI</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>CORONEL PORTILLO</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>MANANTAY</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>-8.408309</t>
@@ -1096,40 +1036,35 @@
       <c r="I13" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>250107</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>250107</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CORONEL_PORTILLO</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>MANANTAY</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>I-255347</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>250107</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>UCAYALI</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>CORONEL PORTILLO</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>MANANTAY</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>-8.435271</t>
@@ -1148,40 +1083,35 @@
       <c r="I14" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>250107</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>250107</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CORONEL_PORTILLO</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>MANANTAY</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>I-255345</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>250107</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>UCAYALI</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>CORONEL PORTILLO</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>MANANTAY</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>-8.4373081</t>
@@ -1200,40 +1130,35 @@
       <c r="I15" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>250107</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>250107</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CORONEL_PORTILLO</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>MANANTAY</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>I-255344</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>250107</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>UCAYALI</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>CORONEL PORTILLO</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>MANANTAY</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>-8.4317467</t>
@@ -1252,40 +1177,35 @@
       <c r="I16" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>250107</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>250107</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CORONEL_PORTILLO</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>MANANTAY</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>I-255343</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>250107</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>UCAYALI</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>CORONEL PORTILLO</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>MANANTAY</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>-8.4332729</t>
@@ -1304,40 +1224,35 @@
       <c r="I17" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>250107</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>250107</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CORONEL_PORTILLO</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>MANANTAY</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>I-255336</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>250107</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>UCAYALI</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>CORONEL PORTILLO</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>MANANTAY</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>-8.4203477</t>
@@ -1356,40 +1271,35 @@
       <c r="I18" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>250107</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>250107</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>CORONEL_PORTILLO</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>MANANTAY</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>I-263081</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>250107</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>UCAYALI</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>CORONEL PORTILLO</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>MANANTAY</t>
-        </is>
-      </c>
       <c r="F19" t="inlineStr">
         <is>
           <t>-8.549242</t>
@@ -1408,40 +1318,35 @@
       <c r="I19" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>250107</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>250107</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CORONEL_PORTILLO</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>MANANTAY</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>I-255377</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>250107</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>UCAYALI</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>CORONEL PORTILLO</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>MANANTAY</t>
-        </is>
-      </c>
       <c r="F20" t="inlineStr">
         <is>
           <t>-8.4279031</t>
@@ -1460,40 +1365,35 @@
       <c r="I20" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>250107</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>250107</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>CORONEL_PORTILLO</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>MANANTAY</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>I-255378</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>250107</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>UCAYALI</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>CORONEL PORTILLO</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>MANANTAY</t>
-        </is>
-      </c>
       <c r="F21" t="inlineStr">
         <is>
           <t>-8.429883</t>
@@ -1512,40 +1412,35 @@
       <c r="I21" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>250107</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>250107</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>CORONEL_PORTILLO</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>MANANTAY</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>I-255379</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>250107</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>UCAYALI</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>CORONEL PORTILLO</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>MANANTAY</t>
-        </is>
-      </c>
       <c r="F22" t="inlineStr">
         <is>
           <t>-8.4349401</t>
@@ -1564,40 +1459,35 @@
       <c r="I22" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>250107</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>250107</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>CORONEL_PORTILLO</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>MANANTAY</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>I-255381</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>250107</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>UCAYALI</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>CORONEL PORTILLO</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>MANANTAY</t>
-        </is>
-      </c>
       <c r="F23" t="inlineStr">
         <is>
           <t>-8.425312</t>
@@ -1616,40 +1506,35 @@
       <c r="I23" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>250107</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>250107</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>CORONEL_PORTILLO</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>MANANTAY</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>I-263082</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>250107</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>UCAYALI</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>CORONEL PORTILLO</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>MANANTAY</t>
-        </is>
-      </c>
       <c r="F24" t="inlineStr">
         <is>
           <t>-8.5500674</t>
@@ -1668,40 +1553,35 @@
       <c r="I24" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>250107</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>250107</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>CORONEL_PORTILLO</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>MANANTAY</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>I-8353</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>250107</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>UCAYALI</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>CORONEL PORTILLO</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>MANANTAY</t>
-        </is>
-      </c>
       <c r="F25" t="inlineStr">
         <is>
           <t>-8.3970341</t>
@@ -1720,40 +1600,35 @@
       <c r="I25" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>250107</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>250107</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>CORONEL_PORTILLO</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>MANANTAY</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>I-255365</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>250107</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>UCAYALI</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>CORONEL PORTILLO</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>MANANTAY</t>
-        </is>
-      </c>
       <c r="F26" t="inlineStr">
         <is>
           <t>-8.425688</t>
@@ -1772,40 +1647,35 @@
       <c r="I26" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>250107</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>250107</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>CORONEL_PORTILLO</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>MANANTAY</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>I-255331</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>250107</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>UCAYALI</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>CORONEL PORTILLO</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>MANANTAY</t>
-        </is>
-      </c>
       <c r="F27" t="inlineStr">
         <is>
           <t>-8.4126675</t>
@@ -1824,40 +1694,35 @@
       <c r="I27" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>250107</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>250107</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>CORONEL_PORTILLO</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>MANANTAY</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
           <t>I-255332</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>250107</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>UCAYALI</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>CORONEL PORTILLO</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>MANANTAY</t>
-        </is>
-      </c>
       <c r="F28" t="inlineStr">
         <is>
           <t>-8.4151389</t>
@@ -1876,40 +1741,35 @@
       <c r="I28" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>250107</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>250107</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>CORONEL_PORTILLO</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>MANANTAY</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
           <t>I-255334</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>250107</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>UCAYALI</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>CORONEL PORTILLO</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>MANANTAY</t>
-        </is>
-      </c>
       <c r="F29" t="inlineStr">
         <is>
           <t>-8.4203493</t>
@@ -1928,11 +1788,6 @@
       <c r="I29" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>250107</t>
         </is>
       </c>
     </row>

--- a/Intersecciones/excels/UCAYALI-CORONEL_PORTILLO-MANANTAY.xlsx
+++ b/Intersecciones/excels/UCAYALI-CORONEL_PORTILLO-MANANTAY.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ID_INT</t>
+          <t>Codigo</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">

--- a/Intersecciones/excels/UCAYALI-CORONEL_PORTILLO-MANANTAY.xlsx
+++ b/Intersecciones/excels/UCAYALI-CORONEL_PORTILLO-MANANTAY.xlsx
@@ -488,7 +488,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -535,7 +535,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -582,7 +582,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -629,7 +629,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -817,7 +817,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1005,7 +1005,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1381,7 +1381,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1475,7 +1475,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1522,7 +1522,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1757,7 +1757,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CORONEL_PORTILLO</t>
+          <t>CORONEL PORTILLO</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">

--- a/Intersecciones/excels/UCAYALI-CORONEL_PORTILLO-MANANTAY.xlsx
+++ b/Intersecciones/excels/UCAYALI-CORONEL_PORTILLO-MANANTAY.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,51 +413,51 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>DEPARTAMENTO</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>PROVINCIA</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>DISTRITO</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Codigo</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>LATITUD</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>LONGITUD</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Vias</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Siniestro_fatal</t>
         </is>
@@ -1786,6 +1774,288 @@
         </is>
       </c>
       <c r="I29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>250107</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>CORONEL PORTILLO</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>MANANTAY</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>I-20941</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>-8.398109</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-74.536437</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>AV. BELLAVISTA CON JR. LOS MANGOS</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>250107</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>CORONEL PORTILLO</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>MANANTAY</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>I-20947</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>-8.3969878</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-74.540362</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>AV. AGUAYTIA CON JR. LOS MANGOS</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>250107</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>CORONEL PORTILLO</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>MANANTAY</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>I-21175</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>-8.4043072</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-74.5481275</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>AV. COLONIZACION CON JR. LOS LAURELES</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>250107</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>CORONEL PORTILLO</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>MANANTAY</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>I-21185</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>-8.4079413</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-74.5519099</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>JR. TOMAS DAVILA SANDOVAL CON JR. LOS CETICOS</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>250107</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>CORONEL PORTILLO</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>MANANTAY</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>I-128394</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>-8.4054987</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-74.5526599</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>JR. LOS LAURELES CON JR. TOMAS DAVILA SANDOVAL</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>250107</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>CORONEL PORTILLO</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>MANANTAY</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>I-133136</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>-8.4003934</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-74.5408913</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>AV. AGUAYTIA CON AV. TUPAC AMARU</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
         <is>
           <t>0</t>
         </is>

--- a/Intersecciones/excels/UCAYALI-CORONEL_PORTILLO-MANANTAY.xlsx
+++ b/Intersecciones/excels/UCAYALI-CORONEL_PORTILLO-MANANTAY.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:I45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2061,6 +2061,476 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>250107</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>CORONEL PORTILLO</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>MANANTAY</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>I-20979</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>-8.3989333</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-74.5375053</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>JR. LOS CETICOS CON JR. BOLOGNESI</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>250107</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>CORONEL PORTILLO</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>MANANTAY</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>I-254773</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>-8.4048674</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-74.5502508</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>JR. LOS LAURELES, CON JR. LAS MERCEDES</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>250107</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>CORONEL PORTILLO</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>MANANTAY</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>I-22132</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>-8.4098027</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>-74.5579005</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>JR. LOS CETICOS CON JR. 12 DE OCTUBRE</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>250107</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>CORONEL PORTILLO</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>MANANTAY</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>I-129419</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>-8.4035272</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>-74.5656594</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>AV. FORESTACION CON JR. SANTIAGO SABOYA</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>250107</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>CORONEL PORTILLO</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>MANANTAY</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>I-27874</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>-8.4085999</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-74.5642615</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>JR. LOS LAURELES CON JR. SANTIAGO SABOYA</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>250107</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>CORONEL PORTILLO</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>MANANTAY</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>I-21298</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>-8.4080915</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>-74.5622549</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>JR. LOS LAURELES CON JR. PACHACUTEC</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>250107</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>CORONEL PORTILLO</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>MANANTAY</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>I-21028</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>-8.4038587</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>-74.5465247</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>JR. LOS LAURELES CON JR. LOS OLIVOS</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>250107</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>CORONEL PORTILLO</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>MANANTAY</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>I-341782</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>-8.4075745</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>-74.5604483</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>AV. AVIACIÓN CON JR. LOS LAURELES</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>250107</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>CORONEL PORTILLO</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>MANANTAY</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>I-27891</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>-8.4006131</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>-74.5710042</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>AV. TUPAC AMARU CON AV. PRIMAVERA</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>250107</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>UCAYALI</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>CORONEL PORTILLO</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>MANANTAY</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>I-22155</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>-8.4066346</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>-74.5569283</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>JR. LOS LAURELES CON JR. LAS MELINAS</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Intersecciones/excels/UCAYALI-CORONEL_PORTILLO-MANANTAY.xlsx
+++ b/Intersecciones/excels/UCAYALI-CORONEL_PORTILLO-MANANTAY.xlsx
@@ -486,22 +486,22 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>I-20988</t>
+          <t>I-8353</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-8.4008518</t>
+          <t>-8.3970341</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-74.5388106</t>
+          <t>-74.5490772</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Atalaya / Avenida Túpac Amaru</t>
+          <t>Avenida Colonización / Calle s / n</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -533,27 +533,27 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>I-132509</t>
+          <t>I-341782</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-8.3996103</t>
+          <t>-8.4075745</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-74.5347843</t>
+          <t>-74.5604483</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Los Ceticos / Calle s / n</t>
+          <t>calle sn / calle s/n</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -580,22 +580,22 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>I-20959</t>
+          <t>I-27891</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-8.3966189</t>
+          <t>-8.4006131</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-74.5331103</t>
+          <t>-74.5710042</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Las Palmeras / Calle s / n</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -627,22 +627,22 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>I-254761</t>
+          <t>I-27874</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-8.3998756</t>
+          <t>-8.4085999</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-74.5429416</t>
+          <t>-74.5642615</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Avenida Túpac Amaru / Calle s / n</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -674,22 +674,22 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>I-255363</t>
+          <t>I-263082</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-8.4286936</t>
+          <t>-8.5500674</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-74.5723062</t>
+          <t>-74.3639573</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Habilitación Urbana Municipal / Calle s / n</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -721,17 +721,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>I-255361</t>
+          <t>I-263081</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-8.4290844</t>
+          <t>-8.549242</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-74.5736614</t>
+          <t>-74.363363</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -768,22 +768,22 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>I-255360</t>
+          <t>I-255381</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-8.426421</t>
+          <t>-8.425312</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-74.5720761</t>
+          <t>-74.5733048</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Habilitación Urbana Municipal / Calle s / n</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -815,17 +815,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>I-255359</t>
+          <t>I-255379</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-8.4272363</t>
+          <t>-8.4349401</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-74.57492</t>
+          <t>-74.5713123</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -862,17 +862,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>I-255358</t>
+          <t>I-255378</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-8.4286205</t>
+          <t>-8.429883</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-74.5774125</t>
+          <t>-74.5727296</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -909,17 +909,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>I-255356</t>
+          <t>I-255377</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-8.4281068</t>
+          <t>-8.4279031</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-74.5765927</t>
+          <t>-74.5733124</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -956,17 +956,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>I-255349</t>
+          <t>I-255365</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-8.4268849</t>
+          <t>-8.425688</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-74.5735978</t>
+          <t>-74.5746229</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1003,22 +1003,22 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>I-255330</t>
+          <t>I-255363</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-8.408309</t>
+          <t>-8.4286936</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-74.5603664</t>
+          <t>-74.5723062</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Avenida Aviación / Calle s / n</t>
+          <t>Habilitación Urbana Municipal / Calle s / n</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1050,17 +1050,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>I-255347</t>
+          <t>I-255361</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-8.435271</t>
+          <t>-8.4290844</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-74.5725605</t>
+          <t>-74.5736614</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1097,17 +1097,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>I-255345</t>
+          <t>I-255360</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-8.4373081</t>
+          <t>-8.426421</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-74.5719764</t>
+          <t>-74.5720761</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1144,17 +1144,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>I-255344</t>
+          <t>I-255359</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-8.4317467</t>
+          <t>-8.4272363</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-74.5735649</t>
+          <t>-74.57492</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1191,17 +1191,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>I-255343</t>
+          <t>I-255358</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-8.4332729</t>
+          <t>-8.4286205</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-74.5731073</t>
+          <t>-74.5774125</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1238,17 +1238,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>I-255336</t>
+          <t>I-255356</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-8.4203477</t>
+          <t>-8.4281068</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-74.5481956</t>
+          <t>-74.5765927</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1285,17 +1285,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>I-263081</t>
+          <t>I-255349</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-8.549242</t>
+          <t>-8.4268849</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-74.363363</t>
+          <t>-74.5735978</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1332,17 +1332,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>I-255377</t>
+          <t>I-255347</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-8.4279031</t>
+          <t>-8.435271</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-74.5733124</t>
+          <t>-74.5725605</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1379,17 +1379,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>I-255378</t>
+          <t>I-255345</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-8.429883</t>
+          <t>-8.4373081</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-74.5727296</t>
+          <t>-74.5719764</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1426,17 +1426,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>I-255379</t>
+          <t>I-255344</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-8.4349401</t>
+          <t>-8.4317467</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-74.5713123</t>
+          <t>-74.5735649</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1473,22 +1473,22 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>I-255381</t>
+          <t>I-255343</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-8.425312</t>
+          <t>-8.4332729</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-74.5733048</t>
+          <t>-74.5731073</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Habilitación Urbana Municipal / Calle s / n</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1520,17 +1520,17 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>I-263082</t>
+          <t>I-255336</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-8.5500674</t>
+          <t>-8.4203477</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-74.3639573</t>
+          <t>-74.5481956</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1567,22 +1567,22 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>I-8353</t>
+          <t>I-255334</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-8.3970341</t>
+          <t>-8.4203493</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-74.5490772</t>
+          <t>-74.5468338</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Avenida Colonización / Calle s / n</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1614,17 +1614,17 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>I-255365</t>
+          <t>I-255332</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-8.425688</t>
+          <t>-8.4151389</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-74.5746229</t>
+          <t>-74.5553027</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>I-255332</t>
+          <t>I-255330</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-8.4151389</t>
+          <t>-8.408309</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-74.5553027</t>
+          <t>-74.5603664</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Avenida Aviación / Calle s / n</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1755,17 +1755,17 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>I-255334</t>
+          <t>I-254773</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-8.4203493</t>
+          <t>-8.4048674</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-74.5468338</t>
+          <t>-74.5502508</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1802,22 +1802,22 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>I-20941</t>
+          <t>I-254761</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-8.398109</t>
+          <t>-8.3998756</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-74.536437</t>
+          <t>-74.5429416</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>AV. BELLAVISTA CON JR. LOS MANGOS</t>
+          <t>Avenida Túpac Amaru / Calle s / n</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1849,22 +1849,22 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>I-20947</t>
+          <t>I-22155</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-8.3969878</t>
+          <t>-8.4066346</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-74.540362</t>
+          <t>-74.5569283</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>AV. AGUAYTIA CON JR. LOS MANGOS</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1896,22 +1896,22 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>I-21175</t>
+          <t>I-22132</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-8.4043072</t>
+          <t>-8.4098027</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-74.5481275</t>
+          <t>-74.5579005</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>AV. COLONIZACION CON JR. LOS LAURELES</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1943,22 +1943,22 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>I-21185</t>
+          <t>I-21298</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-8.4079413</t>
+          <t>-8.4080915</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-74.5519099</t>
+          <t>-74.5622549</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>JR. TOMAS DAVILA SANDOVAL CON JR. LOS CETICOS</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -1990,22 +1990,22 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>I-128394</t>
+          <t>I-21185</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-8.4054987</t>
+          <t>-8.4079413</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-74.5526599</t>
+          <t>-74.5519099</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>JR. LOS LAURELES CON JR. TOMAS DAVILA SANDOVAL</t>
+          <t>JR. TOMAS DAVILA SANDOVAL CON JR. LOS CETICOS</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2037,22 +2037,22 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>I-133136</t>
+          <t>I-21175</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-8.4003934</t>
+          <t>-8.4043072</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-74.5408913</t>
+          <t>-74.5481275</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>AV. AGUAYTIA CON AV. TUPAC AMARU</t>
+          <t>AV. COLONIZACION CON JR. LOS LAURELES</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2084,22 +2084,22 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>I-20979</t>
+          <t>I-21028</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-8.3989333</t>
+          <t>-8.4038587</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-74.5375053</t>
+          <t>-74.5465247</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>JR. LOS CETICOS CON JR. BOLOGNESI</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2131,22 +2131,22 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>I-254773</t>
+          <t>I-20988</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-8.4048674</t>
+          <t>-8.4008518</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-74.5502508</t>
+          <t>-74.5388106</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>JR. LOS LAURELES, CON JR. LAS MERCEDES</t>
+          <t>Atalaya / Avenida Túpac Amaru</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2178,22 +2178,22 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>I-22132</t>
+          <t>I-20979</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-8.4098027</t>
+          <t>-8.3989333</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-74.5579005</t>
+          <t>-74.5375053</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>JR. LOS CETICOS CON JR. 12 DE OCTUBRE</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2225,22 +2225,22 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>I-129419</t>
+          <t>I-20959</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-8.4035272</t>
+          <t>-8.3966189</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-74.5656594</t>
+          <t>-74.5331103</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>AV. FORESTACION CON JR. SANTIAGO SABOYA</t>
+          <t>Las Palmeras / Calle s / n</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2272,22 +2272,22 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>I-27874</t>
+          <t>I-20947</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-8.4085999</t>
+          <t>-8.3969878</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-74.5642615</t>
+          <t>-74.540362</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>JR. LOS LAURELES CON JR. SANTIAGO SABOYA</t>
+          <t>AV. AGUAYTIA CON JR. LOS MANGOS</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2319,22 +2319,22 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>I-21298</t>
+          <t>I-20941</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-8.4080915</t>
+          <t>-8.398109</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-74.5622549</t>
+          <t>-74.536437</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>JR. LOS LAURELES CON JR. PACHACUTEC</t>
+          <t>AV. BELLAVISTA CON JR. LOS MANGOS</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2366,22 +2366,22 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>I-21028</t>
+          <t>I-133136</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-8.4038587</t>
+          <t>-8.4003934</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-74.5465247</t>
+          <t>-74.5408913</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>JR. LOS LAURELES CON JR. LOS OLIVOS</t>
+          <t>AV. AGUAYTIA CON AV. TUPAC AMARU</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2413,27 +2413,27 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>I-341782</t>
+          <t>I-132509</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-8.4075745</t>
+          <t>-8.3996103</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-74.5604483</t>
+          <t>-74.5347843</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>AV. AVIACIÓN CON JR. LOS LAURELES</t>
+          <t>Los Ceticos / Calle s / n</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2460,22 +2460,22 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>I-27891</t>
+          <t>I-129419</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-8.4006131</t>
+          <t>-8.4035272</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-74.5710042</t>
+          <t>-74.5656594</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>AV. TUPAC AMARU CON AV. PRIMAVERA</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2507,22 +2507,22 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>I-22155</t>
+          <t>I-128394</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-8.4066346</t>
+          <t>-8.4054987</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-74.5569283</t>
+          <t>-74.5526599</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>JR. LOS LAURELES CON JR. LAS MELINAS</t>
+          <t>JR. LOS LAURELES CON JR. TOMAS DAVILA SANDOVAL</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
